--- a/docs/test-cases/SPM-49_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-49_Test_Cases.xlsx
@@ -37,8 +37,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -162,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +190,9 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1553,7 +1557,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Coordinator's GET /api/events/EVT-000085/equipment -&gt; HTTP 200. Portable Stage row: quantityReserved=2, status=reserved.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1561,7 +1569,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1569,7 +1581,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1577,7 +1593,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1585,7 +1605,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1723,7 +1745,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Partner Lunch BEFORE: chip=available, 4 total − 0 in maintenance − 0 reserved elsewhere = 4 available for these dates. AFTER Product Demo Day reserves 3: chip=partial, 4 total − 0 in maintenance − 3 reserved elsewhere = 1 available for these dates, '2 requested, 1 available.'</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1731,7 +1757,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1739,7 +1769,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1747,7 +1781,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1755,7 +1793,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1889,7 +1929,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Board Retreat (2027-04-26), unrelated to Sales Kickoff's reservation: chip=available, 4 total − 0 in maintenance − 0 reserved elsewhere = 4 available for these dates.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1897,7 +1941,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1905,7 +1953,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1913,7 +1965,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1921,7 +1977,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2056,7 +2114,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Media Briefing (day after Trade Show's Return Day): chip=partial, 4 total − 0 in maintenance − 3 reserved elsewhere = 1 available for these dates, '2 requested, 1 available.'</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2064,7 +2126,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2072,7 +2138,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2080,7 +2150,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2088,7 +2162,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2222,7 +2298,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Wrap Party (two days after Careers Day's Return Day): chip=available, 4 total − 0 in maintenance − 0 reserved elsewhere = 4 available for these dates.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2230,7 +2310,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2238,7 +2322,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2246,7 +2334,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2254,7 +2346,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2387,7 +2481,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>After Innovation Day reserves 3: Reserved=3, breakdown 4 total − 0 in maintenance − 0 reserved elsewhere = 4 available for these dates (own reservation not counted as held elsewhere).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2395,7 +2493,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2403,7 +2505,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2411,7 +2517,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2419,7 +2529,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2550,7 +2662,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Before attempting: chip=unavailable, 2 total − 0 in maintenance − 2 reserved elsewhere = 0 available for these dates. Reserve attempt -&gt; HTTP 400 {'error': 'Nothing is available for these dates any more.'}.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2558,7 +2674,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2566,7 +2686,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2574,7 +2698,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2582,7 +2710,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2715,7 +2845,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Before: chip=partial, 4 total − 0 in maintenance − 3 reserved elsewhere = 1 available for these dates. Reserve -&gt; HTTP 200. After: Reserved=1 (not 2), status=partially_fulfilled.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2723,7 +2857,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2731,7 +2869,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2739,7 +2881,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2747,7 +2893,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2880,7 +3028,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Concurrent POST reserve, Pop-up Store (Vikram) -&gt; HTTP 200, Flash Sale (Chloe) -&gt; HTTP 400. Exactly one succeeded: Pop-up Store Reserved=1, Flash Sale Reserved=None.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2888,7 +3040,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2896,7 +3052,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Executed as two concurrent API calls, not two browser windows - the same server-side lock is exercised either way; the on-screen refusal message can still be eyeballed once.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2904,7 +3064,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2912,7 +3076,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3044,7 +3210,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Before: chip=partial, 5 total − 2 in maintenance − 0 reserved elsewhere = 3 available for these dates. After reserving: Reserved=3 (not 4), status=partially_fulfilled.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3052,7 +3222,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3060,7 +3234,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3068,7 +3246,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3076,7 +3258,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3331,7 +3515,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Reserve attempt on a Cancelled event -&gt; HTTP 400 {'error': 'This event is cancelled — equipment can no longer be reserved.'}. Reserved stays None.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3339,7 +3527,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3347,7 +3539,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3355,7 +3551,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3363,7 +3563,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3499,7 +3701,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Day 1: chip=unavailable, 4 total − 0 in maintenance − 4 reserved elsewhere = 0 available for these dates. Day 2 reserve -&gt; HTTP 200, Reserved=2, status=reserved. Day 1 reserve attempt -&gt; HTTP 400 {'error': 'Nothing is available for these dates any more.'}.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3507,7 +3713,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3515,7 +3725,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3523,7 +3737,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3531,7 +3749,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3664,7 +3884,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as chloe.teo, GET availability -&gt; HTTP 200. Portable Stage line: Reserved=3, status=reserved, 6 total − 0 in maintenance − 0 reserved elsewhere = 6 available for these dates.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3672,7 +3896,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3680,7 +3908,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3688,7 +3920,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3696,7 +3932,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3826,7 +4064,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as the Organiser rachel.ng, GET availability -&gt; HTTP 403 {'error': 'Only Technical Support Staff can check equipment availability'}.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3834,7 +4076,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3842,7 +4088,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3850,7 +4100,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3858,7 +4112,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3992,7 +4248,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Reserve call -&gt; HTTP 200. After: Reserved=3, status=reserved, 6 total − 0 in maintenance − 0 reserved elsewhere = 6 available for these dates</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4000,7 +4260,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4008,7 +4272,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4016,7 +4284,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4024,7 +4296,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4157,7 +4431,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Reserve call -&gt; HTTP 200. After: Reserved=2, status=partially_fulfilled, 2 total − 0 in maintenance − 0 reserved elsewhere = 2 available for these dates</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4165,7 +4443,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4173,7 +4455,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4181,7 +4467,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4189,7 +4479,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4320,7 +4612,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>GET availability as Coordinator -&gt; HTTP 403 ({'error': 'Only Technical Support Staff can check equipment availability'}). POST reserve as Coordinator -&gt; HTTP 403 ({'error': 'Only Technical Support Staff can reserve equipment'}).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4328,7 +4624,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4336,7 +4636,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4344,7 +4648,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4352,7 +4660,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4485,7 +4795,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Portable Stage: HTTP 200, Reserved=2 (reserved). Ring Light: HTTP 200, Reserved=2 (partially_fulfilled). Mobile Charging Cart: HTTP 400 {'error': 'Nothing is available for these dates any more.'}, Reserved stays None.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4493,7 +4807,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4501,7 +4819,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4509,7 +4831,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4517,7 +4843,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4650,7 +4978,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>After reserving and re-reading (reload): equipment=Portable Stage, Reserved=2, status=reserved.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4658,7 +4990,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4666,7 +5002,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4674,7 +5014,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4682,7 +5026,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4815,7 +5161,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Requested 5, available 6 before reserving. After: Reserved=5 (not 6), status=reserved.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4823,7 +5173,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4831,7 +5185,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4839,7 +5197,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4847,7 +5209,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4981,7 +5345,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Harvest Fair after reserving: Reserved=2. Summer Fair (unrelated date): Reserved=None, status=under_review.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4989,7 +5357,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4997,7 +5369,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -5005,7 +5381,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -5013,7 +5393,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="15" t="n">
+        <v>46292</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-cases/SPM-49_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-49_Test_Cases.xlsx
@@ -3473,8 +3473,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No Reserve button is offered, or clicking it shows the message 'This event is cancelled - equipment can no longer be reserved.' and nothing is reserved.
-The Reserved box stays empty.</t>
+          <t>No Reserve button is offered on the Portable Stage line, and the page shows the message 'This event is cancelled — equipment can no longer be reserved.'
+Nothing is reserved: the Reserved box stays empty.</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A confirmation that the reservation was saved is shown.
+          <t>The message 'Reservation saved: 3 reserved.' appears on the Portable Stage line.
 The Reserved box on the Portable Stage line shows 3.
 The request status chip shows 'Reserved'.</t>
         </is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A confirmation that the reservation was saved is shown.
+          <t>The message 'Reservation saved: 2 reserved.' appears on the Ring Light line.
 The Reserved box on the Ring Light line shows 2 - the smaller of requested (4) and available (2), never more than either.
 The request status chip shows 'Partially fulfilled'.</t>
         </is>
